--- a/doc/2025-03-13-PCB-Doc.xlsx
+++ b/doc/2025-03-13-PCB-Doc.xlsx
@@ -1,20 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\local_repositories\unified-btc-reverse\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robertzakjr 1/Library/CloudStorage/GoogleDrive-robert.zak@comcast.net/My Drive/local_repositories/unified-btc-reverse/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{406B2E05-969E-49B2-B7DE-4A0180CB54D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E80B1D9C-F56B-A845-B3A9-D78124720A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24750" yWindow="30" windowWidth="21945" windowHeight="12900" activeTab="1" xr2:uid="{25DE80F5-B7AB-4270-97E5-DFA9947B1042}"/>
+    <workbookView xWindow="41880" yWindow="680" windowWidth="30120" windowHeight="17580" activeTab="3" xr2:uid="{25DE80F5-B7AB-4270-97E5-DFA9947B1042}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
     <sheet name="CircuitBoardRevisions" sheetId="2" r:id="rId2"/>
+    <sheet name="BTC-7E-HP5 TP" sheetId="3" r:id="rId3"/>
+    <sheet name="Chart1" sheetId="6" r:id="rId4"/>
+    <sheet name="MeasuredVoltageXfer" sheetId="4" r:id="rId5"/>
+    <sheet name="Sheet3" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="45">
   <si>
     <t>Documenting PCB Attributes for Trail Cameras</t>
   </si>
@@ -79,6 +83,99 @@
   </si>
   <si>
     <t>Version</t>
+  </si>
+  <si>
+    <t>78E-HP5_MAIN</t>
+  </si>
+  <si>
+    <t>220919_V3_1</t>
+  </si>
+  <si>
+    <t>SN</t>
+  </si>
+  <si>
+    <t>12010152809237HP5</t>
+  </si>
+  <si>
+    <t>BTC-7E-HP5</t>
+  </si>
+  <si>
+    <t>20210826_V2_0</t>
+  </si>
+  <si>
+    <t>Test Point</t>
+  </si>
+  <si>
+    <t>Volts</t>
+  </si>
+  <si>
+    <t>actua voltage</t>
+  </si>
+  <si>
+    <t>reported voltage</t>
+  </si>
+  <si>
+    <t>Cutuout</t>
+  </si>
+  <si>
+    <t>Voltage Algorithm</t>
+  </si>
+  <si>
+    <t>Battery Voltage</t>
+  </si>
+  <si>
+    <t>R111</t>
+  </si>
+  <si>
+    <t>Ohms</t>
+  </si>
+  <si>
+    <t>Voltage to ADC</t>
+  </si>
+  <si>
+    <t>R???</t>
+  </si>
+  <si>
+    <t>Idle Current</t>
+  </si>
+  <si>
+    <t>ADC REF</t>
+  </si>
+  <si>
+    <t>ADC_Value</t>
+  </si>
+  <si>
+    <t>Working Camera</t>
+  </si>
+  <si>
+    <t>Broken Camera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">at </t>
+  </si>
+  <si>
+    <t>13.6 volts</t>
+  </si>
+  <si>
+    <t>Measured</t>
+  </si>
+  <si>
+    <t>2.0 volts</t>
+  </si>
+  <si>
+    <t>on both cameras!  WTF?</t>
+  </si>
+  <si>
+    <t>ADC Value</t>
+  </si>
+  <si>
+    <t>x500</t>
+  </si>
+  <si>
+    <t>ivar2</t>
+  </si>
+  <si>
+    <t>/ivar2</t>
   </si>
 </sst>
 </file>
@@ -114,9 +211,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -132,6 +232,1230 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2000"/>
+              <a:t>Converting</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="2000" baseline="0"/>
+              <a:t> Battery ADC Value to Voltage w/ Corrupted VOLTCALIB.BIN File</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="2000"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>MeasuredVoltageXfer!$A$4:$A$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>10.9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11.1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11.36</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>11.35</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11.6</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>11.7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11.8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11.9</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>12.2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>12.3</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>12.4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>12.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>12.6</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>12.7</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>12.8</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>12.9</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>13.1</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>13.2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>13.3</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>13.4</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>13.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>13.6</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>13.7</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>13.8</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>13.9</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>14</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>MeasuredVoltageXfer!$B$4:$B$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>648.36</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>618.36</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>578.36</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>548.36</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>483.36</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>503.36</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>438.36</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>408.36</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>368.36</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>348.36</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>308.36</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>278.36</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>248.36</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>213.36</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>183.36</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>138.36000000000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>98.36</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>68.36</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>38.36</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.36</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>628.72</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>598.36</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>568.36</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>528.72</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>483.72</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>448.72</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>423.72</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>383.72</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>353.72</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>323.72000000000003</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>288.72000000000003</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>253.72</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A34E-7D48-B5A8-92B2F3B2ADB8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="668407248"/>
+        <c:axId val="258685296"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="668407248"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400"/>
+                  <a:t>Actual Voltage (Volts)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="258685296"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="258685296"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1600"/>
+                  <a:t>Camera</a:t>
+                </a:r>
+              </a:p>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1600"/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1600" baseline="0"/>
+                  <a:t> Reported Voltage</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" sz="1600"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="668407248"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{BFA266EC-FB13-4743-8596-18AEFD372F04}">
+  <sheetPr/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</chartsheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="0" y="0"/>
+    <xdr:ext cx="8676640" cy="6289040"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E185B6D-5D48-8BB4-439B-20BD826D4D3B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -452,17 +1776,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AEC5BAB-DD92-4D29-8F0E-339C35BA3998}">
   <dimension ref="A2:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>45729</v>
       </c>
@@ -480,17 +1804,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FDF7164-95D0-4095-BB8F-7BD422136E89}">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" customWidth="1"/>
-    <col min="2" max="2" width="17.140625" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5" customWidth="1"/>
+    <col min="2" max="2" width="17.1640625" customWidth="1"/>
+    <col min="3" max="3" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -509,8 +1834,11 @@
       <c r="F1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -530,7 +1858,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -548,6 +1876,1600 @@
       </c>
       <c r="F3">
         <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1">
+        <v>44823</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="1">
+        <v>44434</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50A10CBE-E661-A54E-B7D2-679029AECFB3}">
+  <dimension ref="A2:C52"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>3.2</v>
+      </c>
+      <c r="C40" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDD9302A-F7D8-494D-B9AA-C29B1FCBB364}">
+  <dimension ref="A2:B35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>10.8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>10.9</v>
+      </c>
+      <c r="B4">
+        <v>648.36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>618.36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>11.1</v>
+      </c>
+      <c r="B6">
+        <v>578.36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>11.2</v>
+      </c>
+      <c r="B7">
+        <v>548.36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>11.36</v>
+      </c>
+      <c r="B8">
+        <v>483.36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>11.35</v>
+      </c>
+      <c r="B9">
+        <v>503.36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>11.5</v>
+      </c>
+      <c r="B10">
+        <v>438.36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>11.6</v>
+      </c>
+      <c r="B11">
+        <v>408.36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11.7</v>
+      </c>
+      <c r="B12">
+        <v>368.36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>11.8</v>
+      </c>
+      <c r="B13">
+        <v>348.36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>11.9</v>
+      </c>
+      <c r="B14">
+        <v>308.36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15">
+        <v>278.36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>12.1</v>
+      </c>
+      <c r="B16">
+        <v>248.36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>12.2</v>
+      </c>
+      <c r="B17">
+        <v>213.36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>12.3</v>
+      </c>
+      <c r="B18">
+        <v>183.36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>12.4</v>
+      </c>
+      <c r="B19">
+        <v>138.36000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>12.5</v>
+      </c>
+      <c r="B20">
+        <v>98.36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>12.6</v>
+      </c>
+      <c r="B21">
+        <v>68.36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>12.7</v>
+      </c>
+      <c r="B22">
+        <v>38.36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>12.8</v>
+      </c>
+      <c r="B23">
+        <v>8.36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>12.9</v>
+      </c>
+      <c r="B24">
+        <v>628.72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>13</v>
+      </c>
+      <c r="B25">
+        <v>598.36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>13.1</v>
+      </c>
+      <c r="B26">
+        <v>568.36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>13.2</v>
+      </c>
+      <c r="B27">
+        <v>528.72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>13.3</v>
+      </c>
+      <c r="B28">
+        <v>483.72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>13.4</v>
+      </c>
+      <c r="B29">
+        <v>448.72</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>13.5</v>
+      </c>
+      <c r="B30">
+        <v>423.72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>13.6</v>
+      </c>
+      <c r="B31">
+        <v>383.72</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>13.7</v>
+      </c>
+      <c r="B32">
+        <v>353.72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>13.8</v>
+      </c>
+      <c r="B33">
+        <v>323.72000000000003</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>13.9</v>
+      </c>
+      <c r="B34">
+        <v>288.72000000000003</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>14</v>
+      </c>
+      <c r="B35">
+        <v>253.72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{951E8E45-F2CE-9D49-95AD-03E6547BE71C}">
+  <dimension ref="A1:F56"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1275000</v>
+      </c>
+      <c r="C3" s="2">
+        <v>5100000</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="2">
+        <v>850000</v>
+      </c>
+      <c r="C4" s="2">
+        <v>998300</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="2">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>15</v>
+      </c>
+      <c r="B10" s="3">
+        <f>A10*B$4/(B$4+B$3)</f>
+        <v>6</v>
+      </c>
+      <c r="C10" s="3">
+        <f>A10*C$4/(C$4+C$3)</f>
+        <v>2.4555203909286196</v>
+      </c>
+      <c r="D10" s="2">
+        <f>A10/(C$3+B$4)</f>
+        <v>2.5210084033613444E-6</v>
+      </c>
+      <c r="E10" s="4">
+        <f>(C10/B$5)*2^12</f>
+        <v>1005.7811521243626</v>
+      </c>
+      <c r="F10">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <f>A10-0.2</f>
+        <v>14.8</v>
+      </c>
+      <c r="B11" s="3">
+        <f t="shared" ref="B11:B45" si="0">A11*B$4/(B$4+B$3)</f>
+        <v>5.92</v>
+      </c>
+      <c r="C11" s="3">
+        <f t="shared" ref="C11:C45" si="1">A11*C$4/(C$4+C$3)</f>
+        <v>2.422780119049571</v>
+      </c>
+      <c r="D11" s="2">
+        <f>A11/(C$3+B$4)</f>
+        <v>2.4873949579831934E-6</v>
+      </c>
+      <c r="E11" s="4">
+        <f>(C11/B$5)*2^12</f>
+        <v>992.37073676270427</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <f t="shared" ref="A12:A45" si="2">A11-0.2</f>
+        <v>14.600000000000001</v>
+      </c>
+      <c r="B12" s="3">
+        <f t="shared" si="0"/>
+        <v>5.8400000000000007</v>
+      </c>
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>2.3900398471705233</v>
+      </c>
+      <c r="D12" s="2">
+        <f>A12/(C$3+B$4)</f>
+        <v>2.4537815126050424E-6</v>
+      </c>
+      <c r="E12" s="4">
+        <f t="shared" ref="E12:E45" si="3">(C12/B$5)*2^12</f>
+        <v>978.96032140104637</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <f t="shared" si="2"/>
+        <v>14.400000000000002</v>
+      </c>
+      <c r="B13" s="3">
+        <f t="shared" si="0"/>
+        <v>5.7600000000000007</v>
+      </c>
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>2.3572995752914752</v>
+      </c>
+      <c r="D13" s="2">
+        <f>A13/(C$3+B$4)</f>
+        <v>2.4201680672268909E-6</v>
+      </c>
+      <c r="E13" s="4">
+        <f t="shared" si="3"/>
+        <v>965.54990603938825</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <f t="shared" si="2"/>
+        <v>14.200000000000003</v>
+      </c>
+      <c r="B14" s="3">
+        <f t="shared" si="0"/>
+        <v>5.6800000000000006</v>
+      </c>
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>2.324559303412427</v>
+      </c>
+      <c r="D14" s="2">
+        <f>A14/(C$3+B$4)</f>
+        <v>2.3865546218487399E-6</v>
+      </c>
+      <c r="E14" s="4">
+        <f t="shared" si="3"/>
+        <v>952.13949067773012</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <f t="shared" si="2"/>
+        <v>14.000000000000004</v>
+      </c>
+      <c r="B15" s="3">
+        <f t="shared" si="0"/>
+        <v>5.6000000000000014</v>
+      </c>
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>2.2918190315333788</v>
+      </c>
+      <c r="D15" s="2">
+        <f>A15/(C$3+B$4)</f>
+        <v>2.3529411764705889E-6</v>
+      </c>
+      <c r="E15" s="4">
+        <f t="shared" si="3"/>
+        <v>938.729075316072</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <f t="shared" si="2"/>
+        <v>13.800000000000004</v>
+      </c>
+      <c r="B16" s="3">
+        <f t="shared" si="0"/>
+        <v>5.5200000000000014</v>
+      </c>
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>2.2590787596543307</v>
+      </c>
+      <c r="D16" s="2">
+        <f>A16/(C$3+B$4)</f>
+        <v>2.3193277310924378E-6</v>
+      </c>
+      <c r="E16" s="4">
+        <f t="shared" si="3"/>
+        <v>925.31865995441387</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <f t="shared" si="2"/>
+        <v>13.600000000000005</v>
+      </c>
+      <c r="B17" s="3">
+        <f t="shared" si="0"/>
+        <v>5.4400000000000022</v>
+      </c>
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>2.2263384877752825</v>
+      </c>
+      <c r="D17" s="2">
+        <f>A17/(C$3+B$4)</f>
+        <v>2.2857142857142864E-6</v>
+      </c>
+      <c r="E17" s="4">
+        <f t="shared" si="3"/>
+        <v>911.90824459275575</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <f t="shared" si="2"/>
+        <v>13.400000000000006</v>
+      </c>
+      <c r="B18" s="3">
+        <f t="shared" si="0"/>
+        <v>5.360000000000003</v>
+      </c>
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>2.1935982158962344</v>
+      </c>
+      <c r="D18" s="2">
+        <f>A18/(C$3+B$4)</f>
+        <v>2.2521008403361354E-6</v>
+      </c>
+      <c r="E18" s="4">
+        <f t="shared" si="3"/>
+        <v>898.49782923109763</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <f t="shared" si="2"/>
+        <v>13.200000000000006</v>
+      </c>
+      <c r="B19" s="3">
+        <f t="shared" si="0"/>
+        <v>5.2800000000000029</v>
+      </c>
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>2.1608579440171862</v>
+      </c>
+      <c r="D19" s="2">
+        <f>A19/(C$3+B$4)</f>
+        <v>2.2184873949579843E-6</v>
+      </c>
+      <c r="E19" s="4">
+        <f t="shared" si="3"/>
+        <v>885.0874138694395</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <f t="shared" si="2"/>
+        <v>13.000000000000007</v>
+      </c>
+      <c r="B20" s="3">
+        <f t="shared" si="0"/>
+        <v>5.2000000000000028</v>
+      </c>
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>2.1281176721381381</v>
+      </c>
+      <c r="D20" s="2">
+        <f>A20/(C$3+B$4)</f>
+        <v>2.1848739495798333E-6</v>
+      </c>
+      <c r="E20" s="4">
+        <f t="shared" si="3"/>
+        <v>871.67699850778138</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <f t="shared" si="2"/>
+        <v>12.800000000000008</v>
+      </c>
+      <c r="B21" s="3">
+        <f t="shared" si="0"/>
+        <v>5.1200000000000037</v>
+      </c>
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>2.0953774002590899</v>
+      </c>
+      <c r="D21" s="2">
+        <f>A21/(C$3+B$4)</f>
+        <v>2.1512605042016819E-6</v>
+      </c>
+      <c r="E21" s="4">
+        <f t="shared" si="3"/>
+        <v>858.26658314612325</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <f t="shared" si="2"/>
+        <v>12.600000000000009</v>
+      </c>
+      <c r="B22" s="3">
+        <f t="shared" si="0"/>
+        <v>5.0400000000000036</v>
+      </c>
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>2.0626371283800418</v>
+      </c>
+      <c r="D22" s="2">
+        <f>A22/(C$3+B$4)</f>
+        <v>2.1176470588235308E-6</v>
+      </c>
+      <c r="E22" s="4">
+        <f t="shared" si="3"/>
+        <v>844.85616778446513</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <f t="shared" si="2"/>
+        <v>12.400000000000009</v>
+      </c>
+      <c r="B23" s="3">
+        <f t="shared" si="0"/>
+        <v>4.9600000000000035</v>
+      </c>
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>2.0298968565009936</v>
+      </c>
+      <c r="D23" s="2">
+        <f>A23/(C$3+B$4)</f>
+        <v>2.0840336134453798E-6</v>
+      </c>
+      <c r="E23" s="4">
+        <f t="shared" si="3"/>
+        <v>831.445752422807</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <f t="shared" si="2"/>
+        <v>12.20000000000001</v>
+      </c>
+      <c r="B24" s="3">
+        <f t="shared" si="0"/>
+        <v>4.8800000000000043</v>
+      </c>
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>1.9971565846219455</v>
+      </c>
+      <c r="D24" s="2">
+        <f>A24/(C$3+B$4)</f>
+        <v>2.0504201680672284E-6</v>
+      </c>
+      <c r="E24" s="4">
+        <f t="shared" si="3"/>
+        <v>818.03533706114888</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <f t="shared" si="2"/>
+        <v>12.000000000000011</v>
+      </c>
+      <c r="B25" s="3">
+        <f t="shared" si="0"/>
+        <v>4.8000000000000043</v>
+      </c>
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>1.9644163127428973</v>
+      </c>
+      <c r="D25" s="2">
+        <f>A25/(C$3+B$4)</f>
+        <v>2.0168067226890773E-6</v>
+      </c>
+      <c r="E25" s="4">
+        <f t="shared" si="3"/>
+        <v>804.62492169949076</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <f t="shared" si="2"/>
+        <v>11.800000000000011</v>
+      </c>
+      <c r="B26" s="3">
+        <f t="shared" si="0"/>
+        <v>4.7200000000000042</v>
+      </c>
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>1.9316760408638491</v>
+      </c>
+      <c r="D26" s="2">
+        <f>A26/(C$3+B$4)</f>
+        <v>1.9831932773109263E-6</v>
+      </c>
+      <c r="E26" s="4">
+        <f t="shared" si="3"/>
+        <v>791.21450633783263</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <f t="shared" si="2"/>
+        <v>11.600000000000012</v>
+      </c>
+      <c r="B27" s="3">
+        <f t="shared" si="0"/>
+        <v>4.640000000000005</v>
+      </c>
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>1.8989357689848008</v>
+      </c>
+      <c r="D27" s="2">
+        <f>A27/(C$3+B$4)</f>
+        <v>1.9495798319327753E-6</v>
+      </c>
+      <c r="E27" s="4">
+        <f t="shared" si="3"/>
+        <v>777.80409097617439</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <f t="shared" si="2"/>
+        <v>11.400000000000013</v>
+      </c>
+      <c r="B28" s="3">
+        <f t="shared" si="0"/>
+        <v>4.5600000000000049</v>
+      </c>
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>1.8661954971057528</v>
+      </c>
+      <c r="D28" s="2">
+        <f>A28/(C$3+B$4)</f>
+        <v>1.9159663865546238E-6</v>
+      </c>
+      <c r="E28" s="4">
+        <f t="shared" si="3"/>
+        <v>764.39367561451638</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <f t="shared" si="2"/>
+        <v>11.200000000000014</v>
+      </c>
+      <c r="B29" s="3">
+        <f t="shared" si="0"/>
+        <v>4.4800000000000049</v>
+      </c>
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>1.8334552252267047</v>
+      </c>
+      <c r="D29" s="2">
+        <f>A29/(C$3+B$4)</f>
+        <v>1.8823529411764728E-6</v>
+      </c>
+      <c r="E29" s="4">
+        <f t="shared" si="3"/>
+        <v>750.98326025285826</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <f t="shared" si="2"/>
+        <v>11.000000000000014</v>
+      </c>
+      <c r="B30" s="3">
+        <f t="shared" si="0"/>
+        <v>4.4000000000000057</v>
+      </c>
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>1.8007149533476567</v>
+      </c>
+      <c r="D30" s="2">
+        <f>A30/(C$3+B$4)</f>
+        <v>1.8487394957983218E-6</v>
+      </c>
+      <c r="E30" s="4">
+        <f t="shared" si="3"/>
+        <v>737.57284489120025</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <f t="shared" si="2"/>
+        <v>10.800000000000015</v>
+      </c>
+      <c r="B31" s="3">
+        <f t="shared" si="0"/>
+        <v>4.3200000000000065</v>
+      </c>
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>1.7679746814686084</v>
+      </c>
+      <c r="D31" s="2">
+        <f>A31/(C$3+B$4)</f>
+        <v>1.8151260504201705E-6</v>
+      </c>
+      <c r="E31" s="4">
+        <f t="shared" si="3"/>
+        <v>724.16242952954201</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <f t="shared" si="2"/>
+        <v>10.600000000000016</v>
+      </c>
+      <c r="B32" s="3">
+        <f t="shared" si="0"/>
+        <v>4.2400000000000064</v>
+      </c>
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>1.7352344095895602</v>
+      </c>
+      <c r="D32" s="2">
+        <f>A32/(C$3+B$4)</f>
+        <v>1.7815126050420195E-6</v>
+      </c>
+      <c r="E32" s="4">
+        <f t="shared" si="3"/>
+        <v>710.75201416788389</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <f t="shared" si="2"/>
+        <v>10.400000000000016</v>
+      </c>
+      <c r="B33" s="3">
+        <f t="shared" si="0"/>
+        <v>4.1600000000000064</v>
+      </c>
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>1.7024941377105123</v>
+      </c>
+      <c r="D33" s="2">
+        <f>A33/(C$3+B$4)</f>
+        <v>1.7478991596638683E-6</v>
+      </c>
+      <c r="E33" s="4">
+        <f t="shared" si="3"/>
+        <v>697.34159880622587</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <f t="shared" si="2"/>
+        <v>10.200000000000017</v>
+      </c>
+      <c r="B34" s="3">
+        <f t="shared" si="0"/>
+        <v>4.0800000000000072</v>
+      </c>
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>1.6697538658314639</v>
+      </c>
+      <c r="D34" s="2">
+        <f>A34/(C$3+B$4)</f>
+        <v>1.7142857142857172E-6</v>
+      </c>
+      <c r="E34" s="4">
+        <f t="shared" si="3"/>
+        <v>683.93118344456764</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <f>A34-0.2</f>
+        <v>10.000000000000018</v>
+      </c>
+      <c r="B35" s="3">
+        <f t="shared" si="0"/>
+        <v>4.0000000000000071</v>
+      </c>
+      <c r="C35" s="3">
+        <f t="shared" si="1"/>
+        <v>1.637013593952416</v>
+      </c>
+      <c r="D35" s="2">
+        <f>A35/(C$3+B$4)</f>
+        <v>1.680672268907566E-6</v>
+      </c>
+      <c r="E35" s="4">
+        <f t="shared" si="3"/>
+        <v>670.52076808290963</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <f t="shared" si="2"/>
+        <v>9.8000000000000185</v>
+      </c>
+      <c r="B36" s="3">
+        <f t="shared" si="0"/>
+        <v>3.9200000000000075</v>
+      </c>
+      <c r="C36" s="3">
+        <f t="shared" si="1"/>
+        <v>1.6042733220733678</v>
+      </c>
+      <c r="D36" s="2">
+        <f>A36/(C$3+B$4)</f>
+        <v>1.647058823529415E-6</v>
+      </c>
+      <c r="E36" s="4">
+        <f t="shared" si="3"/>
+        <v>657.1103527212515</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <f t="shared" si="2"/>
+        <v>9.6000000000000192</v>
+      </c>
+      <c r="B37" s="3">
+        <f t="shared" si="0"/>
+        <v>3.8400000000000079</v>
+      </c>
+      <c r="C37" s="3">
+        <f t="shared" si="1"/>
+        <v>1.5715330501943194</v>
+      </c>
+      <c r="D37" s="2">
+        <f>A37/(C$3+B$4)</f>
+        <v>1.6134453781512637E-6</v>
+      </c>
+      <c r="E37" s="4">
+        <f t="shared" si="3"/>
+        <v>643.69993735959326</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <f t="shared" si="2"/>
+        <v>9.4000000000000199</v>
+      </c>
+      <c r="B38" s="3">
+        <f t="shared" si="0"/>
+        <v>3.7600000000000078</v>
+      </c>
+      <c r="C38" s="3">
+        <f t="shared" si="1"/>
+        <v>1.5387927783152715</v>
+      </c>
+      <c r="D38" s="2">
+        <f>A38/(C$3+B$4)</f>
+        <v>1.5798319327731125E-6</v>
+      </c>
+      <c r="E38" s="4">
+        <f t="shared" si="3"/>
+        <v>630.28952199793525</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <f t="shared" si="2"/>
+        <v>9.2000000000000206</v>
+      </c>
+      <c r="B39" s="3">
+        <f t="shared" si="0"/>
+        <v>3.6800000000000082</v>
+      </c>
+      <c r="C39" s="3">
+        <f t="shared" si="1"/>
+        <v>1.5060525064362233</v>
+      </c>
+      <c r="D39" s="2">
+        <f>A39/(C$3+B$4)</f>
+        <v>1.5462184873949615E-6</v>
+      </c>
+      <c r="E39" s="4">
+        <f t="shared" si="3"/>
+        <v>616.87910663627713</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <f t="shared" si="2"/>
+        <v>9.0000000000000213</v>
+      </c>
+      <c r="B40" s="3">
+        <f t="shared" si="0"/>
+        <v>3.6000000000000085</v>
+      </c>
+      <c r="C40" s="3">
+        <f t="shared" si="1"/>
+        <v>1.473312234557175</v>
+      </c>
+      <c r="D40" s="2">
+        <f>A40/(C$3+B$4)</f>
+        <v>1.5126050420168102E-6</v>
+      </c>
+      <c r="E40" s="4">
+        <f t="shared" si="3"/>
+        <v>603.46869127461889</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <f t="shared" si="2"/>
+        <v>8.800000000000022</v>
+      </c>
+      <c r="B41" s="3">
+        <f t="shared" si="0"/>
+        <v>3.5200000000000089</v>
+      </c>
+      <c r="C41" s="3">
+        <f t="shared" si="1"/>
+        <v>1.440571962678127</v>
+      </c>
+      <c r="D41" s="2">
+        <f>A41/(C$3+B$4)</f>
+        <v>1.4789915966386592E-6</v>
+      </c>
+      <c r="E41" s="4">
+        <f t="shared" si="3"/>
+        <v>590.05827591296088</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <f t="shared" si="2"/>
+        <v>8.6000000000000227</v>
+      </c>
+      <c r="B42" s="3">
+        <f t="shared" si="0"/>
+        <v>3.4400000000000093</v>
+      </c>
+      <c r="C42" s="3">
+        <f t="shared" si="1"/>
+        <v>1.4078316907990789</v>
+      </c>
+      <c r="D42" s="2">
+        <f>A42/(C$3+B$4)</f>
+        <v>1.445378151260508E-6</v>
+      </c>
+      <c r="E42" s="4">
+        <f t="shared" si="3"/>
+        <v>576.64786055130276</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <f t="shared" si="2"/>
+        <v>8.4000000000000234</v>
+      </c>
+      <c r="B43" s="3">
+        <f t="shared" si="0"/>
+        <v>3.3600000000000092</v>
+      </c>
+      <c r="C43" s="3">
+        <f t="shared" si="1"/>
+        <v>1.3750914189200307</v>
+      </c>
+      <c r="D43" s="2">
+        <f>A43/(C$3+B$4)</f>
+        <v>1.4117647058823569E-6</v>
+      </c>
+      <c r="E43" s="4">
+        <f t="shared" si="3"/>
+        <v>563.23744518964463</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <f t="shared" si="2"/>
+        <v>8.2000000000000242</v>
+      </c>
+      <c r="B44" s="3">
+        <f t="shared" si="0"/>
+        <v>3.2800000000000096</v>
+      </c>
+      <c r="C44" s="3">
+        <f t="shared" si="1"/>
+        <v>1.3423511470409826</v>
+      </c>
+      <c r="D44" s="2">
+        <f>A44/(C$3+B$4)</f>
+        <v>1.3781512605042057E-6</v>
+      </c>
+      <c r="E44" s="4">
+        <f t="shared" si="3"/>
+        <v>549.82702982798651</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <f t="shared" si="2"/>
+        <v>8.0000000000000249</v>
+      </c>
+      <c r="B45" s="3">
+        <f t="shared" si="0"/>
+        <v>3.2000000000000099</v>
+      </c>
+      <c r="C45" s="3">
+        <f t="shared" si="1"/>
+        <v>1.3096108751619344</v>
+      </c>
+      <c r="D45" s="2">
+        <f>A45/(C$3+B$4)</f>
+        <v>1.3445378151260547E-6</v>
+      </c>
+      <c r="E45" s="4">
+        <f t="shared" si="3"/>
+        <v>536.41661446632838</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>41</v>
+      </c>
+      <c r="B52">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>42</v>
+      </c>
+      <c r="B53">
+        <f>B52*500</f>
+        <v>411500</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>43</v>
+      </c>
+      <c r="B54">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>44</v>
+      </c>
+      <c r="B55">
+        <f>TRUNC(B53/B54, 0)</f>
+        <v>514</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>800</v>
+      </c>
+      <c r="B56">
+        <f>B55+A56</f>
+        <v>1314</v>
       </c>
     </row>
   </sheetData>
